--- a/output/reports/cv_experiment_SVC_qcut_classification.xlsx
+++ b/output/reports/cv_experiment_SVC_qcut_classification.xlsx
@@ -491,19 +491,19 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>855.2856223583221</v>
+        <v>0.09575986862182617</v>
       </c>
       <c r="E2" t="n">
-        <v>0.8780279696355544</v>
+        <v>0.9788327554767209</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8844692171269318</v>
+        <v>0.987012987012987</v>
       </c>
       <c r="G2" t="n">
-        <v>0.8834054991099123</v>
+        <v>0.9869579945799458</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9502146654473876</v>
+        <v>0.9977939928729</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -526,19 +526,19 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>1818.534924030304</v>
+        <v>0.1598746776580811</v>
       </c>
       <c r="E3" t="n">
-        <v>0.8846320489711111</v>
+        <v>0.9788200709583792</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8844692171269318</v>
+        <v>0.987012987012987</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8834054991099123</v>
+        <v>0.9869579945799458</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9502146654473876</v>
+        <v>0.9977939928729</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -622,19 +622,19 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>855.2856223583221</v>
+        <v>0.09575986862182617</v>
       </c>
       <c r="E2" t="n">
-        <v>0.8780279696355544</v>
+        <v>0.9788327554767209</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8844692171269318</v>
+        <v>0.987012987012987</v>
       </c>
       <c r="G2" t="n">
-        <v>0.8834054991099123</v>
+        <v>0.9869579945799458</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9502146654473876</v>
+        <v>0.9977939928729</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -657,19 +657,19 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>1818.534924030304</v>
+        <v>0.1598746776580811</v>
       </c>
       <c r="E3" t="n">
-        <v>0.8846320489711111</v>
+        <v>0.9788200709583792</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8844692171269318</v>
+        <v>0.987012987012987</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8834054991099123</v>
+        <v>0.9869579945799458</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9502146654473876</v>
+        <v>0.9977939928729</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>

--- a/output/reports/cv_experiment_SVC_qcut_classification.xlsx
+++ b/output/reports/cv_experiment_SVC_qcut_classification.xlsx
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.09575986862182617</v>
+        <v>7.500268220901489</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9788327554767209</v>
+        <v>0.6069885338222579</v>
       </c>
       <c r="F2" t="n">
-        <v>0.987012987012987</v>
+        <v>0.6610169491525424</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9869579945799458</v>
+        <v>0.6543174317431744</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9977939928729</v>
+        <v>0.856614478598104</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'kernel': 'rbf', 'gamma': 0.1, 'class_weight': None, 'C': 10}</t>
+          <t>{'C': 10, 'class_weight': 'balanced', 'gamma': 0.1, 'kernel': 'rbf'}</t>
         </is>
       </c>
     </row>
@@ -526,23 +526,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1598746776580811</v>
+        <v>17.0989465713501</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9788200709583792</v>
+        <v>0.6334433676352</v>
       </c>
       <c r="F3" t="n">
-        <v>0.987012987012987</v>
+        <v>0.673728813559322</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9869579945799458</v>
+        <v>0.6586446360153256</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9977939928729</v>
+        <v>0.8314421143349613</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'kernel': 'rbf', 'gamma': 0.1, 'class_weight': None, 'C': 10}</t>
+          <t>{'C': 100, 'class_weight': None, 'gamma': 0.1, 'kernel': 'rbf'}</t>
         </is>
       </c>
     </row>
@@ -622,23 +622,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.09575986862182617</v>
+        <v>7.500268220901489</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9788327554767209</v>
+        <v>0.6069885338222579</v>
       </c>
       <c r="F2" t="n">
-        <v>0.987012987012987</v>
+        <v>0.6610169491525424</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9869579945799458</v>
+        <v>0.6543174317431744</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9977939928729</v>
+        <v>0.856614478598104</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'kernel': 'rbf', 'gamma': 0.1, 'class_weight': None, 'C': 10}</t>
+          <t>{'C': 10, 'class_weight': 'balanced', 'gamma': 0.1, 'kernel': 'rbf'}</t>
         </is>
       </c>
     </row>
@@ -657,23 +657,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1598746776580811</v>
+        <v>17.0989465713501</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9788200709583792</v>
+        <v>0.6334433676352</v>
       </c>
       <c r="F3" t="n">
-        <v>0.987012987012987</v>
+        <v>0.673728813559322</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9869579945799458</v>
+        <v>0.6586446360153256</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9977939928729</v>
+        <v>0.8314421143349613</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'kernel': 'rbf', 'gamma': 0.1, 'class_weight': None, 'C': 10}</t>
+          <t>{'C': 100, 'class_weight': None, 'gamma': 0.1, 'kernel': 'rbf'}</t>
         </is>
       </c>
     </row>
